--- a/data/reports/2024-05-06/2024-05-06_duplicates.xlsx
+++ b/data/reports/2024-05-06/2024-05-06_duplicates.xlsx
@@ -85,6 +85,49 @@
     <t>filing_url</t>
   </si>
   <si>
+    <t>RMD0004807</t>
+  </si>
+  <si>
+    <t>e-vergent.com, LLC</t>
+  </si>
+  <si>
+    <t>2524 76th St
+Franksville WI 53126</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>United States of America</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>Shawn Tarlo</t>
+  </si>
+  <si>
+    <t>Technical Support Lead</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>2628983786</t>
+  </si>
+  <si>
+    <t>Complete STIR/SHAKEN Implementation</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>2024-04-02</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0004801</t>
   </si>
   <si>
@@ -95,54 +138,11 @@
 Franksville Wisconsin 53126</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>United States of America</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
     <t>null
 null</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=949115a61bc13c102eb2a82fe54bcb0c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004807</t>
-  </si>
-  <si>
-    <t>e-vergent.com, LLC</t>
-  </si>
-  <si>
-    <t>2524 76th St
-Franksville WI 53126</t>
-  </si>
-  <si>
-    <t>Shawn Tarlo</t>
-  </si>
-  <si>
-    <t>Technical Support Lead</t>
-  </si>
-  <si>
-    <t>Support</t>
-  </si>
-  <si>
-    <t>2628983786</t>
-  </si>
-  <si>
-    <t>Complete STIR/SHAKEN Implementation</t>
-  </si>
-  <si>
-    <t>2024-04-02</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005813</t>
@@ -185,7 +185,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004139</t>
+    <t>RMD0009352</t>
   </si>
   <si>
     <t>Global Net Holdings, Inc.</t>
@@ -201,34 +201,56 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>800-7096314</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004139</t>
+  </si>
+  <si>
     <t>Sales</t>
   </si>
   <si>
     <t>800-709-6314</t>
   </si>
   <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009352</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t>800-7096314</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>null
+null CA
+California</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -236,32 +258,10 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>U.S. Virgin Islands</t>
-  </si>
-  <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
-    <t>null
-null CA
-California</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -284,24 +302,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009205</t>
@@ -346,7 +346,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008869</t>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -380,16 +389,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004389</t>
+    <t>RMD0003929</t>
   </si>
   <si>
     <t>Idealtel Dominicana USA, Inc. dba myidealtel.com</t>
@@ -400,13 +400,13 @@
 Cooper City FL 33328</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004389</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9a075a791b8db4109294113d9c4bcbd5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003929</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005819</t>
@@ -493,10 +493,44 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0007488</t>
+  </si>
+  <si>
+    <t>Matchcom Telecommunications Inc.</t>
+  </si>
+  <si>
+    <t>1680 Michigan Ave
+Ste 700
+Miami Beach FL 33139</t>
+  </si>
+  <si>
+    <t>Cesar Luna</t>
+  </si>
+  <si>
+    <t>NOC Manager</t>
+  </si>
+  <si>
+    <t>NOC Department</t>
+  </si>
+  <si>
+    <t>1680 Michigan Avenue
+Suite 700
+Miami FL 33139</t>
+  </si>
+  <si>
+    <t>9544563191</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2023-12-18</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0003758</t>
-  </si>
-  <si>
-    <t>Matchcom Telecommunications Inc.</t>
   </si>
   <si>
     <t>1680 Michigan Ave
@@ -523,40 +557,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007488</t>
-  </si>
-  <si>
-    <t>1680 Michigan Ave
-Ste 700
-Miami Beach FL 33139</t>
-  </si>
-  <si>
-    <t>Cesar Luna</t>
-  </si>
-  <si>
-    <t>NOC Manager</t>
-  </si>
-  <si>
-    <t>NOC Department</t>
-  </si>
-  <si>
-    <t>1680 Michigan Avenue
-Suite 700
-Miami FL 33139</t>
-  </si>
-  <si>
-    <t>9544563191</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2023-12-18</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0004110</t>
   </si>
   <si>
@@ -593,7 +593,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9650dd421bcd38102eb2a82fe54bcb46&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005139</t>
+    <t>RMD0005124</t>
   </si>
   <si>
     <t>Opentact Inc</t>
@@ -604,6 +604,12 @@
 Cheyenne WY 82009</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f40ce7d11b8eb01068d1a82eac4bcbde&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005139</t>
+  </si>
+  <si>
     <t>Anne Kwong</t>
   </si>
   <si>
@@ -626,13 +632,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005124</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f40ce7d11b8eb01068d1a82eac4bcbde&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004701</t>
+    <t>RMD0003052</t>
   </si>
   <si>
     <t>Jaintel LLC</t>
@@ -642,15 +642,33 @@
 DE 19806-3334 Wilmington, United States</t>
   </si>
   <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Elayaraja Jinadoss</t>
   </si>
   <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>'+447341664829</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004701</t>
+  </si>
+  <si>
     <t>Operations Director</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
     <t>'+1 737 237 0913</t>
   </si>
   <si>
@@ -658,24 +676,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b1f3904a1b4138107ccf20ecac4bcbbf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003052</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+447341664829</t>
-  </si>
-  <si>
-    <t>2024-05-01</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0003053</t>
@@ -706,7 +706,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -717,32 +717,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -762,6 +736,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007384</t>
   </si>
   <si>
@@ -790,7 +790,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005040</t>
+    <t>RMD0008577</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -800,31 +800,31 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>BatchDialer</t>
+  </si>
+  <si>
+    <t>Ivo Draginov</t>
+  </si>
+  <si>
+    <t>Product Manager</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>6026220397</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005040</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
-  </si>
-  <si>
-    <t>BatchDialer</t>
-  </si>
-  <si>
-    <t>Ivo Draginov</t>
-  </si>
-  <si>
-    <t>Product Manager</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>6026220397</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005569</t>
+    <t>RMD0005461</t>
   </si>
   <si>
     <t>Valstarr Asia</t>
@@ -834,25 +834,10 @@
 Valley Center CA 92082</t>
   </si>
   <si>
+    <t>0031217672</t>
+  </si>
+  <si>
     <t>Vincent W. Kahn</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Systems Admin</t>
-  </si>
-  <si>
-    <t>'+13213288217</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005461</t>
-  </si>
-  <si>
-    <t>0031217672</t>
   </si>
   <si>
     <t>MANAGER</t>
@@ -872,7 +857,22 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
+    <t>RMD0005569</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Systems Admin</t>
+  </si>
+  <si>
+    <t>'+13213288217</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -885,22 +885,22 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Syed Omar Farooq Shah</t>
+  </si>
+  <si>
+    <t>'+61406851546</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005297</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
-  </si>
-  <si>
-    <t>Syed Omar Farooq Shah</t>
-  </si>
-  <si>
-    <t>'+61406851546</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
+    <t>RMD0005585</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -914,6 +914,28 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
+  </si>
+  <si>
+    <t>Paul Joncas</t>
+  </si>
+  <si>
+    <t>Operatopms</t>
+  </si>
+  <si>
+    <t>187 Plymouth Avenue
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005574</t>
+  </si>
+  <si>
     <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
   </si>
   <si>
@@ -921,29 +943,7 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
-  </si>
-  <si>
-    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
-  </si>
-  <si>
-    <t>Paul Joncas</t>
-  </si>
-  <si>
-    <t>Operatopms</t>
-  </si>
-  <si>
-    <t>187 Plymouth Avenue
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -978,7 +978,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008125</t>
+    <t>RMD0008123</t>
   </si>
   <si>
     <t>Hansen Network Solutions &amp; Services</t>
@@ -989,6 +989,12 @@
 Las Vegas NV 89128</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008125</t>
+  </si>
+  <si>
     <t>JR Jarmillo</t>
   </si>
   <si>
@@ -1001,13 +1007,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9277fe1b7a3810dcd1ed3be54bcb40&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008123</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007575</t>
+    <t>RMD0007626</t>
   </si>
   <si>
     <t>Turcios Parada SA</t>
@@ -1020,16 +1020,16 @@
     <t>El Salvador</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007575</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007626</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007716</t>
+    <t>RMD0007696</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1039,16 +1039,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007716</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1058,6 +1058,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1071,12 +1077,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1110,7 +1110,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1120,12 +1120,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1133,7 +1127,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008612</t>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008611</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1143,6 +1143,18 @@
  110065 Dehli, India</t>
   </si>
   <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>Nobe</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
     <t>India</t>
   </si>
   <si>
@@ -1158,19 +1170,7 @@
     <t>RMD0008610</t>
   </si>
   <si>
-    <t>Bangladesh</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008611</t>
-  </si>
-  <si>
-    <t>Nobe</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008759</t>
@@ -1235,34 +1235,34 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=82b1054a1b0f30508d57ecace54bcbda&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008787</t>
+  </si>
+  <si>
+    <t>Personal Computers Plus</t>
+  </si>
+  <si>
+    <t>0031485048</t>
+  </si>
+  <si>
+    <t>Jeffrey Houston</t>
+  </si>
+  <si>
+    <t>Networking</t>
+  </si>
+  <si>
+    <t>'+16039294272</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3752aec61b0f3050003c43f1f54bcb54&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008786</t>
   </si>
   <si>
-    <t>Personal Computers Plus</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=29f1aec61b0f3050003c43f1f54bcba5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008787</t>
-  </si>
-  <si>
-    <t>0031485048</t>
-  </si>
-  <si>
-    <t>Jeffrey Houston</t>
-  </si>
-  <si>
-    <t>Networking</t>
-  </si>
-  <si>
-    <t>'+16039294272</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3752aec61b0f3050003c43f1f54bcb54&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009161</t>
+    <t>RMD0009160</t>
   </si>
   <si>
     <t>MCE Systems</t>
@@ -1272,16 +1272,16 @@
 Irvine CA 92604</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009161</t>
+  </si>
+  <si>
     <t>9497014500</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009160</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009453</t>
@@ -6054,42 +6054,56 @@
       <c r="I3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="M3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
+      <c r="Q3" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R3" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U3" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="V3" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1">
         <v>16082927</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>26</v>
@@ -6106,40 +6120,26 @@
       <c r="I4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>40</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U4" s="1"/>
       <c r="V4" s="1" t="s">
         <v>41</v>
       </c>
@@ -6236,7 +6236,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -6249,7 +6249,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6275,9 +6275,15 @@
       <c r="F7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J7" s="1" t="s">
         <v>58</v>
       </c>
@@ -6298,10 +6304,10 @@
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>26</v>
@@ -6335,15 +6341,9 @@
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
         <v>58</v>
       </c>
@@ -6364,10 +6364,10 @@
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>26</v>
@@ -6396,7 +6396,7 @@
         <v>70</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>71</v>
@@ -6423,7 +6423,7 @@
         <v>26</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1" t="s">
@@ -6444,7 +6444,7 @@
         <v>76</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>71</v>
@@ -6471,7 +6471,7 @@
         <v>26</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U10" s="1"/>
       <c r="V10" s="1" t="s">
@@ -6518,12 +6518,14 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>26</v>
@@ -6531,14 +6533,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6565,7 +6569,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6574,16 +6578,14 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>26</v>
@@ -6591,9 +6593,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>101</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
@@ -6672,7 +6672,7 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>71</v>
@@ -6697,7 +6697,7 @@
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6723,54 +6723,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6787,33 +6773,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -6844,7 +6844,7 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -6857,7 +6857,7 @@
         <v>26</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U17" s="1"/>
       <c r="V17" s="1" t="s">
@@ -6890,7 +6890,7 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -6903,7 +6903,7 @@
         <v>26</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U18" s="1"/>
       <c r="V18" s="1" t="s">
@@ -6994,7 +6994,7 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -7007,7 +7007,7 @@
         <v>26</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1" t="s">
@@ -7051,7 +7051,7 @@
         <v>26</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U21" s="1" t="s">
         <v>135</v>
@@ -7102,16 +7102,16 @@
       </c>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U22" s="1" t="s">
         <v>142</v>
@@ -7134,7 +7134,7 @@
         <v>146</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>71</v>
@@ -7146,7 +7146,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -7159,7 +7159,7 @@
         <v>26</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U23" s="1"/>
       <c r="V23" s="1" t="s">
@@ -7180,7 +7180,7 @@
         <v>149</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>71</v>
@@ -7192,7 +7192,7 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -7205,7 +7205,7 @@
         <v>26</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1" t="s">
@@ -7252,9 +7252,11 @@
       <c r="O25" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="P25" s="1"/>
+      <c r="P25" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="Q25" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>26</v>
@@ -7263,16 +7265,18 @@
         <v>26</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U25" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>160</v>
+      </c>
       <c r="V25" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B26" s="1">
         <v>27710730</v>
@@ -7281,7 +7285,7 @@
         <v>152</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>26</v>
@@ -7293,28 +7297,26 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>167</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7323,11 +7325,9 @@
         <v>26</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>168</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U26" s="1"/>
       <c r="V26" s="1" t="s">
         <v>169</v>
       </c>
@@ -7364,7 +7364,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -7377,7 +7377,7 @@
         <v>26</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U27" s="1"/>
       <c r="V27" s="1" t="s">
@@ -7419,7 +7419,7 @@
         <v>176</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>177</v>
@@ -7432,10 +7432,10 @@
       </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>26</v>
@@ -7478,47 +7478,33 @@
       <c r="I29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="V29" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B30" s="1">
         <v>30149645</v>
@@ -7544,26 +7530,40 @@
       <c r="I30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="M30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
+        <v>189</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>190</v>
+      </c>
       <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
+      <c r="Q30" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R30" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U30" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="V30" s="1" t="s">
         <v>192</v>
       </c>
@@ -7582,55 +7582,61 @@
         <v>195</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J31" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>195</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>27</v>
+        <v>196</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T31" s="1" t="s">
         <v>26</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B32" s="1">
         <v>30758643</v>
@@ -7642,47 +7648,41 @@
         <v>195</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>204</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>195</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>203</v>
+        <v>27</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>205</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T32" s="1" t="s">
         <v>26</v>
@@ -7708,10 +7708,10 @@
         <v>210</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -7720,7 +7720,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -7733,7 +7733,7 @@
         <v>26</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1" t="s">
@@ -7754,10 +7754,10 @@
         <v>210</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -7775,7 +7775,7 @@
         <v>210</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>215</v>
@@ -7785,7 +7785,7 @@
         <v>101</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>26</v>
@@ -7812,7 +7812,7 @@
         <v>219</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>220</v>
@@ -7824,45 +7824,33 @@
       <c r="I35" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>224</v>
-      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>226</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q35" s="1"/>
       <c r="R35" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B36" s="1">
         <v>31064850</v>
@@ -7874,36 +7862,48 @@
         <v>219</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>220</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
       <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
+      <c r="Q36" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R36" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1" t="s">
@@ -7924,7 +7924,7 @@
         <v>234</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>235</v>
@@ -7955,7 +7955,7 @@
         <v>51</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
@@ -7982,7 +7982,7 @@
         <v>234</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>235</v>
@@ -7994,7 +7994,7 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -8007,7 +8007,7 @@
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8035,34 +8035,48 @@
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="I39" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>247</v>
+      </c>
       <c r="M39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
+        <v>243</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>248</v>
+      </c>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
+      <c r="Q39" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R39" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B40" s="1">
         <v>31124688</v>
@@ -8081,39 +8095,25 @@
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>249</v>
-      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>250</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
       <c r="P40" s="1"/>
-      <c r="Q40" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q40" s="1"/>
       <c r="R40" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U40" s="1"/>
       <c r="V40" s="1" t="s">
@@ -8139,48 +8139,54 @@
       <c r="F41" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+      <c r="G41" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J41" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B42" s="1">
         <v>31217029</v>
@@ -8197,26 +8203,20 @@
       <c r="F42" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
       <c r="J42" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>27</v>
@@ -8226,16 +8226,16 @@
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8256,7 +8256,7 @@
         <v>269</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>270</v>
@@ -8264,33 +8264,45 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
+      <c r="J43" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="M43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
+        <v>269</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>272</v>
+      </c>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
+      <c r="Q43" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R43" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B44" s="1">
         <v>31294614</v>
@@ -8302,7 +8314,7 @@
         <v>269</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>270</v>
@@ -8310,36 +8322,24 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>214</v>
-      </c>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>274</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q44" s="1"/>
       <c r="R44" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8371,42 +8371,48 @@
       <c r="H45" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>282</v>
+      </c>
       <c r="M45" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U45" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V45" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B46" s="1">
         <v>31356652</v>
@@ -8427,18 +8433,14 @@
         <v>279</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L46" s="1" t="s">
         <v>287</v>
       </c>
+      <c r="I46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
       <c r="M46" s="1" t="s">
         <v>288</v>
       </c>
@@ -8446,24 +8448,22 @@
         <v>27</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P46" s="1"/>
       <c r="Q46" s="1" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U46" s="1"/>
       <c r="V46" s="1" t="s">
         <v>289</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>291</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>292</v>
@@ -8511,7 +8511,7 @@
         <v>101</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>26</v>
@@ -8536,7 +8536,7 @@
         <v>298</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>292</v>
@@ -8554,7 +8554,7 @@
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -8567,7 +8567,7 @@
         <v>26</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U48" s="1"/>
       <c r="V48" s="1" t="s">
@@ -8588,55 +8588,41 @@
         <v>302</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
-      <c r="J49" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
       <c r="M49" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
       <c r="R49" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S49" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U49" s="1"/>
       <c r="V49" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B50" s="1">
         <v>31394760</v>
@@ -8648,32 +8634,46 @@
         <v>302</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
+      <c r="J50" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="M50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
+        <v>302</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q50" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R50" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U50" s="1"/>
       <c r="V50" s="1" t="s">
@@ -8694,7 +8694,7 @@
         <v>311</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>312</v>
@@ -8705,7 +8705,9 @@
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
+      <c r="M51" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
@@ -8717,7 +8719,7 @@
         <v>26</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U51" s="1"/>
       <c r="V51" s="1" t="s">
@@ -8738,7 +8740,7 @@
         <v>311</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>312</v>
@@ -8749,9 +8751,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
-      <c r="M52" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
@@ -8763,7 +8763,7 @@
         <v>26</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U52" s="1"/>
       <c r="V52" s="1" t="s">
@@ -8784,25 +8784,19 @@
         <v>318</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -8815,7 +8809,7 @@
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
@@ -8836,19 +8830,25 @@
         <v>318</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
@@ -8861,7 +8861,7 @@
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8882,55 +8882,41 @@
         <v>324</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
-      <c r="J55" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
       <c r="R55" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B56" s="1">
         <v>31445216</v>
@@ -8942,32 +8928,46 @@
         <v>324</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
+      <c r="J56" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
+        <v>324</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R56" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U56" s="1"/>
       <c r="V56" s="1" t="s">
@@ -8988,7 +8988,7 @@
         <v>334</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>220</v>
@@ -9000,7 +9000,7 @@
         <v>335</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
@@ -9014,10 +9014,10 @@
       </c>
       <c r="P57" s="1"/>
       <c r="Q57" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>26</v>
@@ -9044,7 +9044,7 @@
         <v>334</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>220</v>
@@ -9056,7 +9056,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -9069,7 +9069,7 @@
         <v>26</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U58" s="1"/>
       <c r="V58" s="1" t="s">
@@ -9090,7 +9090,7 @@
         <v>343</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>71</v>
@@ -9102,7 +9102,7 @@
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1" t="s">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
@@ -9115,16 +9115,16 @@
         <v>26</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U59" s="1"/>
       <c r="V59" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="60" spans="1:22">
       <c r="A60" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B60" s="1">
         <v>31457815</v>
@@ -9136,7 +9136,7 @@
         <v>343</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>71</v>
@@ -9148,7 +9148,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>346</v>
+        <v>40</v>
       </c>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
@@ -9161,7 +9161,7 @@
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
@@ -9182,53 +9182,43 @@
         <v>350</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>351</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
+      <c r="I61" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>353</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="62" spans="1:22">
       <c r="A62" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B62" s="1">
         <v>31475270</v>
@@ -9240,41 +9230,53 @@
         <v>350</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
+      <c r="J62" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="M62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
+        <v>350</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
+      <c r="Q62" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R62" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U62" s="1"/>
       <c r="V62" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="63" spans="1:22">
       <c r="A63" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B63" s="1">
         <v>31475270</v>
@@ -9286,21 +9288,19 @@
         <v>350</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
@@ -9313,7 +9313,7 @@
         <v>26</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U63" s="1"/>
       <c r="V63" s="1" t="s">
@@ -9344,7 +9344,7 @@
         <v>363</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L64" s="1"/>
       <c r="M64" s="1" t="s">
@@ -9363,7 +9363,7 @@
         <v>51</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>26</v>
@@ -9388,7 +9388,7 @@
         <v>362</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>71</v>
@@ -9400,7 +9400,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
@@ -9413,7 +9413,7 @@
         <v>26</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1" t="s">
@@ -9469,7 +9469,7 @@
         <v>51</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>26</v>
@@ -9496,7 +9496,7 @@
         <v>371</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>71</v>
@@ -9510,7 +9510,7 @@
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
@@ -9523,7 +9523,7 @@
         <v>26</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U67" s="1"/>
       <c r="V67" s="1" t="s">
@@ -9544,41 +9544,59 @@
         <v>362</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G68" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>383</v>
+      </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
+      <c r="J68" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>385</v>
+      </c>
       <c r="M68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
+        <v>362</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R68" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U68" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="V68" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="69" spans="1:22">
       <c r="A69" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B69" s="1">
         <v>31491517</v>
@@ -9590,52 +9608,34 @@
         <v>362</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>385</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
-      <c r="J69" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>387</v>
-      </c>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
       <c r="M69" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="P69" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
       <c r="R69" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U69" s="1" t="s">
-        <v>189</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U69" s="1"/>
       <c r="V69" s="1" t="s">
         <v>389</v>
       </c>
@@ -9654,49 +9654,39 @@
         <v>392</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
-      <c r="J70" s="1" t="s">
-        <v>391</v>
-      </c>
+      <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
-      <c r="M70" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>393</v>
-      </c>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
       <c r="P70" s="1"/>
-      <c r="Q70" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q70" s="1"/>
       <c r="R70" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U70" s="1"/>
       <c r="V70" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="71" spans="1:22">
       <c r="A71" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B71" s="1">
         <v>31544182</v>
@@ -9708,30 +9698,40 @@
         <v>392</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+      <c r="J71" s="1" t="s">
+        <v>391</v>
+      </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
+      <c r="M71" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>395</v>
+      </c>
       <c r="P71" s="1"/>
-      <c r="Q71" s="1"/>
+      <c r="Q71" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R71" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S71" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U71" s="1"/>
       <c r="V71" s="1" t="s">
@@ -9752,7 +9752,7 @@
         <v>399</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>235</v>
@@ -9775,7 +9775,7 @@
         <v>26</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U72" s="1"/>
       <c r="V72" s="1" t="s">
@@ -9796,7 +9796,7 @@
         <v>402</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>235</v>
@@ -9808,7 +9808,7 @@
         <v>403</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>404</v>
@@ -9827,7 +9827,7 @@
         <v>101</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S73" s="1" t="s">
         <v>26</v>
@@ -9854,7 +9854,7 @@
         <v>409</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>71</v>
@@ -9877,7 +9877,7 @@
         <v>26</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U74" s="1"/>
       <c r="V74" s="1" t="s">
@@ -9910,7 +9910,7 @@
         <v>412</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>413</v>
@@ -9929,7 +9929,7 @@
         <v>101</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>26</v>
@@ -9960,13 +9960,13 @@
         <v>27</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>418</v>
@@ -9988,10 +9988,10 @@
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>26</v>
@@ -10014,10 +10014,10 @@
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
@@ -10029,11 +10029,11 @@
         <v>59</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M77" s="1"/>
       <c r="N77" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="O77" s="1" t="s">
         <v>425</v>
@@ -10043,7 +10043,7 @@
         <v>101</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S77" s="1" t="s">
         <v>26</v>
@@ -10074,7 +10074,7 @@
         <v>27</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>429</v>
@@ -10105,7 +10105,7 @@
         <v>51</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>26</v>
@@ -10130,10 +10130,10 @@
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>28</v>
@@ -10157,7 +10157,7 @@
         <v>439</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O79" s="1" t="s">
         <v>440</v>
@@ -10167,10 +10167,10 @@
         <v>51</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S79" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T79" s="1" t="s">
         <v>26</v>
@@ -10194,7 +10194,7 @@
         <v>444</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>445</v>
@@ -10213,7 +10213,7 @@
         <v>449</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>444</v>
@@ -10226,10 +10226,10 @@
       </c>
       <c r="P80" s="1"/>
       <c r="Q80" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S80" s="1" t="s">
         <v>26</v>
@@ -10284,10 +10284,10 @@
       </c>
       <c r="P81" s="1"/>
       <c r="Q81" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S81" s="1" t="s">
         <v>26</v>
@@ -10336,10 +10336,10 @@
       </c>
       <c r="P82" s="1"/>
       <c r="Q82" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>26</v>
@@ -10378,7 +10378,7 @@
         <v>469</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>470</v>
@@ -10397,7 +10397,7 @@
         <v>101</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>26</v>
@@ -10436,10 +10436,10 @@
         <v>476</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>474</v>
@@ -10452,10 +10452,10 @@
       </c>
       <c r="P84" s="1"/>
       <c r="Q84" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>26</v>
@@ -10492,7 +10492,7 @@
         <v>481</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L85" s="1" t="s">
         <v>482</v>
@@ -10508,10 +10508,10 @@
       </c>
       <c r="P85" s="1"/>
       <c r="Q85" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S85" s="1" t="s">
         <v>26</v>
@@ -10536,7 +10536,7 @@
         <v>487</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>445</v>
@@ -10551,7 +10551,7 @@
         <v>59</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>487</v>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="P86" s="1"/>
       <c r="Q86" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R86" s="1" t="s">
         <v>26</v>
@@ -10573,7 +10573,7 @@
         <v>26</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U86" s="1"/>
       <c r="V86" s="1" t="s">
@@ -10610,7 +10610,7 @@
         <v>494</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L87" s="1"/>
       <c r="M87" s="1" t="s">
@@ -10633,7 +10633,7 @@
         <v>26</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U87" s="1" t="s">
         <v>496</v>
@@ -10688,10 +10688,10 @@
       </c>
       <c r="P88" s="1"/>
       <c r="Q88" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S88" s="1" t="s">
         <v>26</v>
@@ -10716,7 +10716,7 @@
         <v>506</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>292</v>
@@ -10741,7 +10741,7 @@
         <v>26</v>
       </c>
       <c r="T89" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U89" s="1" t="s">
         <v>508</v>
@@ -10762,7 +10762,7 @@
         <v>511</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>220</v>
@@ -10780,10 +10780,10 @@
         <v>512</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>511</v>
@@ -10799,7 +10799,7 @@
         <v>51</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S90" s="1" t="s">
         <v>26</v>
@@ -10835,10 +10835,10 @@
       </c>
       <c r="I91" s="1"/>
       <c r="J91" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>518</v>
@@ -10854,10 +10854,10 @@
       </c>
       <c r="P91" s="1"/>
       <c r="Q91" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S91" s="1" t="s">
         <v>26</v>
@@ -10882,7 +10882,7 @@
         <v>522</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>523</v>
@@ -10913,7 +10913,7 @@
         <v>101</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S92" s="1" t="s">
         <v>26</v>
@@ -10955,7 +10955,7 @@
         <v>525</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M93" s="1"/>
       <c r="N93" s="1" t="s">
@@ -10972,7 +10972,7 @@
         <v>26</v>
       </c>
       <c r="S93" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T93" s="1" t="s">
         <v>26</v>
@@ -10996,7 +10996,7 @@
         <v>537</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>538</v>
@@ -11011,7 +11011,7 @@
         <v>525</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>537</v>
@@ -11024,10 +11024,10 @@
       </c>
       <c r="P94" s="1"/>
       <c r="Q94" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S94" s="1" t="s">
         <v>26</v>
@@ -11068,10 +11068,10 @@
         <v>546</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M95" s="1" t="s">
         <v>544</v>
@@ -11084,10 +11084,10 @@
       </c>
       <c r="P95" s="1"/>
       <c r="Q95" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S95" s="1" t="s">
         <v>26</v>
@@ -11112,7 +11112,7 @@
         <v>550</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>551</v>
@@ -11126,7 +11126,7 @@
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
       <c r="M96" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
@@ -11139,7 +11139,7 @@
         <v>26</v>
       </c>
       <c r="T96" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U96" s="1"/>
       <c r="V96" s="1" t="s">
@@ -11156,7 +11156,7 @@
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>555</v>
@@ -11182,10 +11182,10 @@
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S97" s="1" t="s">
         <v>26</v>
@@ -11212,7 +11212,7 @@
         <v>563</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>235</v>
@@ -11224,7 +11224,7 @@
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
       <c r="M98" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
@@ -11237,7 +11237,7 @@
         <v>26</v>
       </c>
       <c r="T98" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U98" s="1"/>
       <c r="V98" s="1" t="s">
@@ -11268,7 +11268,7 @@
         <v>567</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L99" s="1" t="s">
         <v>568</v>
@@ -11284,10 +11284,10 @@
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S99" s="1" t="s">
         <v>26</v>
@@ -11330,7 +11330,7 @@
         <v>574</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>98</v>
@@ -11349,7 +11349,7 @@
         <v>101</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S100" s="1" t="s">
         <v>26</v>
@@ -11358,7 +11358,7 @@
         <v>26</v>
       </c>
       <c r="U100" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V100" s="1" t="s">
         <v>576</v>
@@ -11407,7 +11407,7 @@
         <v>101</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S101" s="1" t="s">
         <v>26</v>
@@ -11447,7 +11447,7 @@
         <v>374</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M102" s="1" t="s">
         <v>587</v>
@@ -11460,10 +11460,10 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R102" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S102" s="1" t="s">
         <v>26</v>
@@ -11502,7 +11502,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
@@ -11515,7 +11515,7 @@
         <v>26</v>
       </c>
       <c r="T103" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U103" s="1"/>
       <c r="V103" s="1" t="s">
@@ -11552,7 +11552,7 @@
         <v>596</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>597</v>
@@ -11568,10 +11568,10 @@
       </c>
       <c r="P104" s="1"/>
       <c r="Q104" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R104" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S104" s="1" t="s">
         <v>26</v>
@@ -11598,7 +11598,7 @@
         <v>602</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>235</v>
@@ -11610,7 +11610,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
@@ -11623,7 +11623,7 @@
         <v>26</v>
       </c>
       <c r="T105" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U105" s="1"/>
       <c r="V105" s="1" t="s">
@@ -11672,10 +11672,10 @@
       </c>
       <c r="P106" s="1"/>
       <c r="Q106" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R106" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S106" s="1" t="s">
         <v>26</v>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="P107" s="1"/>
       <c r="Q107" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R107" s="1" t="s">
         <v>26</v>
@@ -11772,10 +11772,10 @@
         <v>620</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M108" s="1" t="s">
         <v>619</v>
@@ -11788,10 +11788,10 @@
       </c>
       <c r="P108" s="1"/>
       <c r="Q108" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S108" s="1" t="s">
         <v>26</v>
@@ -11830,10 +11830,10 @@
         <v>626</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>625</v>
@@ -11849,7 +11849,7 @@
         <v>51</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S109" s="1" t="s">
         <v>26</v>
@@ -11889,7 +11889,7 @@
         <v>632</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>630</v>
@@ -11902,10 +11902,10 @@
       </c>
       <c r="P110" s="1"/>
       <c r="Q110" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S110" s="1" t="s">
         <v>26</v>
@@ -11944,7 +11944,7 @@
         <v>638</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>639</v>
@@ -11960,10 +11960,10 @@
       </c>
       <c r="P111" s="1"/>
       <c r="Q111" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S111" s="1" t="s">
         <v>26</v>
@@ -11986,10 +11986,10 @@
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
@@ -11998,14 +11998,14 @@
         <v>643</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>214</v>
       </c>
       <c r="M112" s="1"/>
       <c r="N112" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O112" s="1" t="s">
         <v>644</v>
@@ -12015,7 +12015,7 @@
         <v>51</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S112" s="1" t="s">
         <v>26</v>
@@ -12057,7 +12057,7 @@
         <v>650</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M113" s="1"/>
       <c r="N113" s="1" t="s">
@@ -12068,10 +12068,10 @@
       </c>
       <c r="P113" s="1"/>
       <c r="Q113" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S113" s="1" t="s">
         <v>26</v>
@@ -12096,7 +12096,7 @@
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>292</v>
@@ -12125,7 +12125,7 @@
         <v>26</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U114" s="1" t="s">
         <v>655</v>
@@ -12144,7 +12144,7 @@
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>292</v>
@@ -12173,7 +12173,7 @@
         <v>26</v>
       </c>
       <c r="T115" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U115" s="1" t="s">
         <v>655</v>
@@ -12206,10 +12206,10 @@
         <v>662</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M116" s="1"/>
       <c r="N116" s="1" t="s">
@@ -12222,10 +12222,10 @@
         <v>664</v>
       </c>
       <c r="Q116" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R116" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S116" s="1" t="s">
         <v>26</v>
@@ -12252,7 +12252,7 @@
         <v>668</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>669</v>
@@ -12289,7 +12289,7 @@
         <v>101</v>
       </c>
       <c r="R117" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S117" s="1" t="s">
         <v>26</v>
@@ -12332,7 +12332,7 @@
         <v>678</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L118" s="1" t="s">
         <v>679</v>
@@ -12348,10 +12348,10 @@
       </c>
       <c r="P118" s="1"/>
       <c r="Q118" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S118" s="1" t="s">
         <v>26</v>
@@ -12402,10 +12402,10 @@
       </c>
       <c r="P119" s="1"/>
       <c r="Q119" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R119" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S119" s="1" t="s">
         <v>26</v>
@@ -12464,10 +12464,10 @@
       </c>
       <c r="P120" s="1"/>
       <c r="Q120" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R120" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S120" s="1" t="s">
         <v>26</v>
@@ -12490,7 +12490,7 @@
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>696</v>
@@ -12513,7 +12513,7 @@
         <v>26</v>
       </c>
       <c r="T121" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U121" s="1" t="s">
         <v>697</v>
@@ -12534,7 +12534,7 @@
         <v>700</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>220</v>
@@ -12551,7 +12551,7 @@
         <v>82</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M122" s="1" t="s">
         <v>700</v>
@@ -12567,7 +12567,7 @@
         <v>101</v>
       </c>
       <c r="R122" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S122" s="1" t="s">
         <v>26</v>
@@ -12592,10 +12592,10 @@
         <v>706</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>28</v>
@@ -12619,17 +12619,17 @@
         <v>706</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O123" s="1" t="s">
         <v>710</v>
       </c>
       <c r="P123" s="1"/>
       <c r="Q123" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R123" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S123" s="1" t="s">
         <v>26</v>
@@ -12672,7 +12672,7 @@
         <v>715</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L124" s="1" t="s">
         <v>404</v>
@@ -12688,10 +12688,10 @@
       </c>
       <c r="P124" s="1"/>
       <c r="Q124" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R124" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S124" s="1" t="s">
         <v>26</v>
@@ -12732,7 +12732,7 @@
         <v>721</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L125" s="1" t="s">
         <v>214</v>
@@ -12746,10 +12746,10 @@
       </c>
       <c r="P125" s="1"/>
       <c r="Q125" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R125" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S125" s="1" t="s">
         <v>26</v>
@@ -12788,7 +12788,7 @@
         <v>726</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L126" s="1" t="s">
         <v>214</v>
@@ -12804,10 +12804,10 @@
       </c>
       <c r="P126" s="1"/>
       <c r="Q126" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R126" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S126" s="1" t="s">
         <v>26</v>
@@ -12830,7 +12830,7 @@
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>730</v>
@@ -12862,10 +12862,10 @@
       </c>
       <c r="P127" s="1"/>
       <c r="Q127" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R127" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S127" s="1" t="s">
         <v>26</v>
@@ -12888,7 +12888,7 @@
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>445</v>
@@ -12911,7 +12911,7 @@
         <v>26</v>
       </c>
       <c r="T128" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U128" s="1" t="s">
         <v>736</v>
@@ -12930,10 +12930,10 @@
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G129" s="1"/>
       <c r="H129" s="1"/>
@@ -12945,11 +12945,11 @@
         <v>581</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M129" s="1"/>
       <c r="N129" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="O129" s="1" t="s">
         <v>740</v>
@@ -12959,7 +12959,7 @@
         <v>51</v>
       </c>
       <c r="R129" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S129" s="1" t="s">
         <v>26</v>
@@ -13021,7 +13021,7 @@
         <v>51</v>
       </c>
       <c r="R130" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S130" s="1" t="s">
         <v>26</v>
@@ -13046,7 +13046,7 @@
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>752</v>
@@ -13063,7 +13063,7 @@
         <v>59</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M131" s="1" t="s">
         <v>755</v>
@@ -13079,7 +13079,7 @@
         <v>101</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S131" s="1" t="s">
         <v>26</v>
@@ -13118,10 +13118,10 @@
         <v>761</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M132" s="1" t="s">
         <v>762</v>
@@ -13137,7 +13137,7 @@
         <v>51</v>
       </c>
       <c r="R132" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S132" s="1" t="s">
         <v>26</v>
@@ -13179,7 +13179,7 @@
         <v>769</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M133" s="1"/>
       <c r="N133" s="1" t="s">
@@ -13190,10 +13190,10 @@
       </c>
       <c r="P133" s="1"/>
       <c r="Q133" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R133" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S133" s="1" t="s">
         <v>26</v>
@@ -13255,7 +13255,7 @@
         <v>51</v>
       </c>
       <c r="R134" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S134" s="1" t="s">
         <v>26</v>
@@ -13286,13 +13286,13 @@
         <v>27</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>781</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
@@ -13309,7 +13309,7 @@
         <v>26</v>
       </c>
       <c r="T135" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U135" s="1"/>
       <c r="V135" s="1" t="s">
@@ -13326,7 +13326,7 @@
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>445</v>
@@ -13356,10 +13356,10 @@
         <v>788</v>
       </c>
       <c r="Q136" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R136" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S136" s="1" t="s">
         <v>26</v>
@@ -13384,7 +13384,7 @@
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>792</v>
@@ -13405,7 +13405,7 @@
         <v>795</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>796</v>
@@ -13418,10 +13418,10 @@
       </c>
       <c r="P137" s="1"/>
       <c r="Q137" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R137" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S137" s="1" t="s">
         <v>26</v>
@@ -13446,10 +13446,10 @@
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>801</v>
@@ -13475,7 +13475,7 @@
         <v>26</v>
       </c>
       <c r="T138" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U138" s="1" t="s">
         <v>804</v>
@@ -13494,7 +13494,7 @@
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>807</v>
@@ -13508,7 +13508,7 @@
         <v>808</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>809</v>
@@ -13525,7 +13525,7 @@
         <v>101</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S139" s="1" t="s">
         <v>26</v>
@@ -13579,7 +13579,7 @@
         <v>51</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S140" s="1" t="s">
         <v>26</v>
@@ -13604,7 +13604,7 @@
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>821</v>
@@ -13625,7 +13625,7 @@
         <v>59</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M141" s="1"/>
       <c r="N141" s="1" t="s">
@@ -13636,10 +13636,10 @@
       </c>
       <c r="P141" s="1"/>
       <c r="Q141" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R141" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S141" s="1" t="s">
         <v>26</v>
@@ -13689,7 +13689,7 @@
         <v>26</v>
       </c>
       <c r="T142" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U142" s="1" t="s">
         <v>829</v>
@@ -13731,7 +13731,7 @@
         <v>26</v>
       </c>
       <c r="T143" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U143" s="1" t="s">
         <v>832</v>
@@ -13777,7 +13777,7 @@
         <v>26</v>
       </c>
       <c r="T144" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U144" s="1" t="s">
         <v>832</v>
@@ -13796,7 +13796,7 @@
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>292</v>
@@ -13821,7 +13821,7 @@
         <v>26</v>
       </c>
       <c r="T145" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U145" s="1" t="s">
         <v>840</v>
@@ -13861,7 +13861,7 @@
         <v>462</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M146" s="1"/>
       <c r="N146" s="1" t="s">
@@ -13875,10 +13875,10 @@
         <v>101</v>
       </c>
       <c r="R146" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S146" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T146" s="1" t="s">
         <v>26</v>
@@ -13930,10 +13930,10 @@
         <v>851</v>
       </c>
       <c r="Q147" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R147" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S147" s="1" t="s">
         <v>26</v>
@@ -13960,7 +13960,7 @@
         <v>854</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>235</v>
@@ -13972,7 +13972,7 @@
       <c r="K148" s="1"/>
       <c r="L148" s="1"/>
       <c r="M148" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
@@ -13985,7 +13985,7 @@
         <v>26</v>
       </c>
       <c r="T148" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U148" s="1"/>
       <c r="V148" s="1" t="s">
@@ -14002,10 +14002,10 @@
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1"/>
@@ -14023,7 +14023,7 @@
         <v>859</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O149" s="1" t="s">
         <v>860</v>
@@ -14033,7 +14033,7 @@
         <v>101</v>
       </c>
       <c r="R149" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S149" s="1" t="s">
         <v>26</v>
@@ -14079,7 +14079,7 @@
         <v>26</v>
       </c>
       <c r="T150" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U150" s="1" t="s">
         <v>863</v>
@@ -14112,10 +14112,10 @@
         <v>867</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>868</v>
@@ -14131,7 +14131,7 @@
         <v>101</v>
       </c>
       <c r="R151" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S151" s="1" t="s">
         <v>26</v>
@@ -14156,7 +14156,7 @@
         <v>872</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>292</v>
@@ -14185,7 +14185,7 @@
         <v>26</v>
       </c>
       <c r="T152" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U152" s="1"/>
       <c r="V152" s="1" t="s">
@@ -14216,10 +14216,10 @@
         <v>876</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M153" s="1"/>
       <c r="N153" s="1" t="s">
@@ -14230,10 +14230,10 @@
       </c>
       <c r="P153" s="1"/>
       <c r="Q153" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R153" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S153" s="1" t="s">
         <v>26</v>
@@ -14256,10 +14256,10 @@
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G154" s="1"/>
       <c r="H154" s="1"/>
@@ -14279,7 +14279,7 @@
         <v>26</v>
       </c>
       <c r="T154" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U154" s="1"/>
       <c r="V154" s="1" t="s">
@@ -14302,7 +14302,7 @@
         <v>27</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
@@ -14321,7 +14321,7 @@
         <v>26</v>
       </c>
       <c r="T155" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U155" s="1" t="s">
         <v>882</v>
@@ -14340,7 +14340,7 @@
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>292</v>
@@ -14368,10 +14368,10 @@
       </c>
       <c r="P156" s="1"/>
       <c r="Q156" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R156" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S156" s="1" t="s">
         <v>26</v>
@@ -14394,7 +14394,7 @@
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>891</v>
@@ -14409,7 +14409,7 @@
         <v>59</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M157" s="1" t="s">
         <v>893</v>
@@ -14425,7 +14425,7 @@
         <v>101</v>
       </c>
       <c r="R157" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S157" s="1" t="s">
         <v>26</v>
@@ -14473,7 +14473,7 @@
         <v>101</v>
       </c>
       <c r="R158" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S158" s="1" t="s">
         <v>26</v>
@@ -14496,7 +14496,7 @@
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>901</v>
@@ -14522,10 +14522,10 @@
       </c>
       <c r="P159" s="1"/>
       <c r="Q159" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S159" s="1" t="s">
         <v>26</v>
@@ -14548,10 +14548,10 @@
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G160" s="1"/>
       <c r="H160" s="1"/>
@@ -14571,7 +14571,7 @@
         <v>26</v>
       </c>
       <c r="T160" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U160" s="1"/>
       <c r="V160" s="1" t="s">
@@ -14588,7 +14588,7 @@
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>445</v>
@@ -14600,10 +14600,10 @@
         <v>908</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M161" s="1" t="s">
         <v>909</v>
@@ -14616,10 +14616,10 @@
       </c>
       <c r="P161" s="1"/>
       <c r="Q161" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R161" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S161" s="1" t="s">
         <v>26</v>
@@ -14642,10 +14642,10 @@
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>28</v>
@@ -14671,7 +14671,7 @@
         <v>26</v>
       </c>
       <c r="T162" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U162" s="1"/>
       <c r="V162" s="1" t="s">
@@ -14722,10 +14722,10 @@
       </c>
       <c r="P163" s="1"/>
       <c r="Q163" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R163" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S163" s="1" t="s">
         <v>26</v>
@@ -14760,10 +14760,10 @@
         <v>922</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M164" s="1" t="s">
         <v>923</v>
@@ -14776,10 +14776,10 @@
       </c>
       <c r="P164" s="1"/>
       <c r="Q164" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R164" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S164" s="1" t="s">
         <v>26</v>
@@ -14814,7 +14814,7 @@
         <v>927</v>
       </c>
       <c r="K165" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L165" s="1" t="s">
         <v>928</v>
@@ -14831,7 +14831,7 @@
         <v>101</v>
       </c>
       <c r="R165" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S165" s="1" t="s">
         <v>26</v>
@@ -14854,7 +14854,7 @@
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>807</v>
@@ -14879,7 +14879,7 @@
         <v>26</v>
       </c>
       <c r="T166" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U166" s="1"/>
       <c r="V166" s="1" t="s">
@@ -14896,7 +14896,7 @@
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>292</v>
@@ -14925,7 +14925,7 @@
         <v>26</v>
       </c>
       <c r="T167" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U167" s="1"/>
       <c r="V167" s="1" t="s">
@@ -14942,10 +14942,10 @@
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
@@ -14963,7 +14963,7 @@
         <v>942</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O168" s="1" t="s">
         <v>943</v>
@@ -14973,7 +14973,7 @@
         <v>101</v>
       </c>
       <c r="R168" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S168" s="1" t="s">
         <v>26</v>
@@ -15014,10 +15014,10 @@
         <v>946</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M169" s="1" t="s">
         <v>947</v>
@@ -15030,10 +15030,10 @@
       </c>
       <c r="P169" s="1"/>
       <c r="Q169" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R169" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S169" s="1" t="s">
         <v>26</v>
@@ -15056,10 +15056,10 @@
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -15068,14 +15068,14 @@
         <v>951</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="L170" s="1" t="s">
         <v>952</v>
       </c>
       <c r="M170" s="1"/>
       <c r="N170" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="O170" s="1" t="s">
         <v>953</v>
@@ -15085,7 +15085,7 @@
         <v>101</v>
       </c>
       <c r="R170" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S170" s="1" t="s">
         <v>26</v>
@@ -15144,10 +15144,10 @@
       </c>
       <c r="P171" s="1"/>
       <c r="Q171" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R171" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S171" s="1" t="s">
         <v>26</v>
@@ -15184,10 +15184,10 @@
         <v>965</v>
       </c>
       <c r="K172" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M172" s="1"/>
       <c r="N172" s="1" t="s">
@@ -15198,10 +15198,10 @@
       </c>
       <c r="P172" s="1"/>
       <c r="Q172" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R172" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S172" s="1" t="s">
         <v>26</v>
@@ -15249,7 +15249,7 @@
         <v>26</v>
       </c>
       <c r="T173" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U173" s="1"/>
       <c r="V173" s="1" t="s">
@@ -15281,7 +15281,7 @@
         <v>59</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M174" s="1"/>
       <c r="N174" s="1" t="s">
@@ -15295,7 +15295,7 @@
         <v>101</v>
       </c>
       <c r="R174" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S174" s="1" t="s">
         <v>26</v>
@@ -15334,7 +15334,7 @@
         <v>977</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="L175" s="1" t="s">
         <v>978</v>
@@ -15348,13 +15348,13 @@
       </c>
       <c r="P175" s="1"/>
       <c r="Q175" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S175" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T175" s="1" t="s">
         <v>26</v>
@@ -15392,10 +15392,10 @@
         <v>985</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M176" s="1" t="s">
         <v>983</v>
@@ -15411,7 +15411,7 @@
         <v>101</v>
       </c>
       <c r="R176" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S176" s="1" t="s">
         <v>26</v>
@@ -15456,10 +15456,10 @@
         <v>991</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>989</v>
@@ -15472,10 +15472,10 @@
       </c>
       <c r="P177" s="1"/>
       <c r="Q177" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R177" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S177" s="1" t="s">
         <v>26</v>
@@ -15506,13 +15506,13 @@
         <v>27</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H178" s="1" t="s">
         <v>996</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J178" s="1" t="s">
         <v>997</v>
@@ -15521,7 +15521,7 @@
         <v>998</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M178" s="1" t="s">
         <v>995</v>
@@ -15536,10 +15536,10 @@
         <v>1000</v>
       </c>
       <c r="Q178" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R178" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S178" s="1" t="s">
         <v>26</v>
@@ -15566,7 +15566,7 @@
         <v>1004</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>292</v>
@@ -15585,7 +15585,7 @@
         <v>462</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M179" s="1" t="s">
         <v>1004</v>
@@ -15601,7 +15601,7 @@
         <v>101</v>
       </c>
       <c r="R179" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S179" s="1" t="s">
         <v>26</v>
@@ -15626,7 +15626,7 @@
         <v>1010</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>292</v>
@@ -15662,10 +15662,10 @@
         <v>1015</v>
       </c>
       <c r="Q180" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R180" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S180" s="1" t="s">
         <v>26</v>
@@ -15692,7 +15692,7 @@
         <v>1018</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>235</v>
@@ -15720,10 +15720,10 @@
       </c>
       <c r="P181" s="1"/>
       <c r="Q181" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R181" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S181" s="1" t="s">
         <v>26</v>
@@ -15754,19 +15754,19 @@
         <v>27</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H182" s="1" t="s">
         <v>1024</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
       <c r="L182" s="1"/>
       <c r="M182" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N182" s="1"/>
       <c r="O182" s="1"/>
@@ -15779,7 +15779,7 @@
         <v>26</v>
       </c>
       <c r="T182" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U182" s="1"/>
       <c r="V182" s="1" t="s">
@@ -15830,10 +15830,10 @@
       </c>
       <c r="P183" s="1"/>
       <c r="Q183" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R183" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S183" s="1" t="s">
         <v>26</v>
@@ -15858,7 +15858,7 @@
         <v>1036</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>1037</v>
@@ -15895,7 +15895,7 @@
         <v>26</v>
       </c>
       <c r="T184" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U184" s="1" t="s">
         <v>1041</v>
@@ -15930,10 +15930,10 @@
         <v>1046</v>
       </c>
       <c r="K185" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M185" s="1" t="s">
         <v>1044</v>
@@ -15955,7 +15955,7 @@
         <v>26</v>
       </c>
       <c r="T185" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U185" s="1" t="s">
         <v>1048</v>
@@ -15989,7 +15989,7 @@
         <v>1052</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M186" s="1"/>
       <c r="N186" s="1" t="s">
@@ -16003,10 +16003,10 @@
         <v>51</v>
       </c>
       <c r="R186" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S186" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T186" s="1" t="s">
         <v>26</v>
@@ -16030,7 +16030,7 @@
         <v>1057</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>821</v>
@@ -16059,7 +16059,7 @@
         <v>101</v>
       </c>
       <c r="R187" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S187" s="1" t="s">
         <v>26</v>
@@ -16084,7 +16084,7 @@
         <v>1063</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>235</v>
@@ -16118,10 +16118,10 @@
       </c>
       <c r="P188" s="1"/>
       <c r="Q188" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R188" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S188" s="1" t="s">
         <v>26</v>
@@ -16146,7 +16146,7 @@
         <v>1071</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>792</v>
@@ -16163,7 +16163,7 @@
         <v>1074</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M189" s="1" t="s">
         <v>1075</v>
@@ -16179,7 +16179,7 @@
         <v>51</v>
       </c>
       <c r="R189" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S189" s="1" t="s">
         <v>26</v>
@@ -16223,7 +16223,7 @@
         <v>59</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M190" s="1" t="s">
         <v>1080</v>
@@ -16236,10 +16236,10 @@
       </c>
       <c r="P190" s="1"/>
       <c r="Q190" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R190" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S190" s="1" t="s">
         <v>26</v>
@@ -16264,7 +16264,7 @@
         <v>1086</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>821</v>
@@ -16282,7 +16282,7 @@
       <c r="K191" s="1"/>
       <c r="L191" s="1"/>
       <c r="M191" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N191" s="1"/>
       <c r="O191" s="1"/>
@@ -16295,7 +16295,7 @@
         <v>26</v>
       </c>
       <c r="T191" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U191" s="1"/>
       <c r="V191" s="1" t="s">
@@ -16320,14 +16320,14 @@
         <v>27</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="H192" s="1" t="s">
         <v>1089</v>
       </c>
       <c r="I192" s="1"/>
       <c r="J192" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K192" s="1" t="s">
         <v>59</v>
@@ -16346,10 +16346,10 @@
       </c>
       <c r="P192" s="1"/>
       <c r="Q192" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R192" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S192" s="1" t="s">
         <v>26</v>
@@ -16417,7 +16417,7 @@
         <v>26</v>
       </c>
       <c r="T193" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U193" s="1"/>
       <c r="V193" s="1" t="s">
@@ -16436,7 +16436,7 @@
         <v>1102</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>1103</v>
@@ -16454,7 +16454,7 @@
         <v>1105</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L194" s="1" t="s">
         <v>1106</v>
@@ -16470,10 +16470,10 @@
       </c>
       <c r="P194" s="1"/>
       <c r="Q194" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R194" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S194" s="1" t="s">
         <v>26</v>
@@ -16514,7 +16514,7 @@
         <v>1114</v>
       </c>
       <c r="K195" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L195" s="1" t="s">
         <v>214</v>
@@ -16530,10 +16530,10 @@
       </c>
       <c r="P195" s="1"/>
       <c r="Q195" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R195" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S195" s="1" t="s">
         <v>26</v>
@@ -16574,10 +16574,10 @@
         <v>1121</v>
       </c>
       <c r="K196" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M196" s="1" t="s">
         <v>1122</v>
@@ -16593,7 +16593,7 @@
         <v>101</v>
       </c>
       <c r="R196" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S196" s="1" t="s">
         <v>26</v>
@@ -16618,7 +16618,7 @@
         <v>1126</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>1127</v>
@@ -16654,10 +16654,10 @@
         <v>1132</v>
       </c>
       <c r="Q197" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R197" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S197" s="1" t="s">
         <v>26</v>
@@ -16682,7 +16682,7 @@
         <v>1135</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>312</v>
@@ -16694,7 +16694,7 @@
       <c r="K198" s="1"/>
       <c r="L198" s="1"/>
       <c r="M198" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N198" s="1"/>
       <c r="O198" s="1"/>
@@ -16707,7 +16707,7 @@
         <v>26</v>
       </c>
       <c r="T198" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U198" s="1"/>
       <c r="V198" s="1" t="s">
@@ -16726,7 +16726,7 @@
         <v>1138</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>292</v>
@@ -16765,7 +16765,7 @@
         <v>26</v>
       </c>
       <c r="T199" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U199" s="1" t="s">
         <v>1048</v>
@@ -16786,7 +16786,7 @@
         <v>1145</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>1146</v>
@@ -16821,7 +16821,7 @@
         <v>101</v>
       </c>
       <c r="R200" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S200" s="1" t="s">
         <v>26</v>
@@ -16846,7 +16846,7 @@
         <v>1152</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>669</v>
@@ -16883,7 +16883,7 @@
         <v>51</v>
       </c>
       <c r="R201" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S201" s="1" t="s">
         <v>26</v>
@@ -16925,7 +16925,7 @@
         <v>1162</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M202" s="1" t="s">
         <v>1159</v>
@@ -16938,10 +16938,10 @@
       </c>
       <c r="P202" s="1"/>
       <c r="Q202" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R202" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S202" s="1" t="s">
         <v>26</v>
@@ -16966,10 +16966,10 @@
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
@@ -16989,7 +16989,7 @@
         <v>26</v>
       </c>
       <c r="T203" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U203" s="1" t="s">
         <v>1166</v>
@@ -17010,7 +17010,7 @@
         <v>1169</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>235</v>
@@ -17022,7 +17022,7 @@
         <v>1170</v>
       </c>
       <c r="K204" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L204" s="1" t="s">
         <v>419</v>
@@ -17041,7 +17041,7 @@
         <v>51</v>
       </c>
       <c r="R204" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S204" s="1" t="s">
         <v>26</v>
@@ -17142,7 +17142,7 @@
         <v>1185</v>
       </c>
       <c r="K206" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L206" s="1"/>
       <c r="M206" s="1" t="s">
@@ -17156,10 +17156,10 @@
       </c>
       <c r="P206" s="1"/>
       <c r="Q206" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R206" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S206" s="1" t="s">
         <v>26</v>
@@ -17184,7 +17184,7 @@
         <v>1189</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>71</v>
@@ -17202,7 +17202,7 @@
       <c r="K207" s="1"/>
       <c r="L207" s="1"/>
       <c r="M207" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
@@ -17215,7 +17215,7 @@
         <v>26</v>
       </c>
       <c r="T207" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U207" s="1"/>
       <c r="V207" s="1" t="s">
@@ -17252,7 +17252,7 @@
         <v>1196</v>
       </c>
       <c r="K208" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L208" s="1" t="s">
         <v>1197</v>
@@ -17268,10 +17268,10 @@
       </c>
       <c r="P208" s="1"/>
       <c r="Q208" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R208" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S208" s="1" t="s">
         <v>26</v>
@@ -17298,7 +17298,7 @@
         <v>1202</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>71</v>
@@ -17312,7 +17312,7 @@
         <v>1204</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L209" s="1"/>
       <c r="M209" s="1" t="s">
@@ -17337,7 +17337,7 @@
         <v>26</v>
       </c>
       <c r="T209" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U209" s="1"/>
       <c r="V209" s="1" t="s">
@@ -17362,13 +17362,13 @@
         <v>27</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>1210</v>
@@ -17377,7 +17377,7 @@
         <v>59</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M210" s="1" t="s">
         <v>1209</v>
@@ -17393,7 +17393,7 @@
         <v>101</v>
       </c>
       <c r="R210" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S210" s="1" t="s">
         <v>26</v>
@@ -17455,7 +17455,7 @@
         <v>101</v>
       </c>
       <c r="R211" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S211" s="1" t="s">
         <v>26</v>
@@ -17490,7 +17490,7 @@
         <v>1221</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J212" s="1" t="s">
         <v>1222</v>
@@ -17515,7 +17515,7 @@
         <v>101</v>
       </c>
       <c r="R212" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S212" s="1" t="s">
         <v>26</v>
@@ -17538,7 +17538,7 @@
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>292</v>
@@ -17570,7 +17570,7 @@
         <v>26</v>
       </c>
       <c r="S213" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T213" s="1" t="s">
         <v>26</v>
@@ -17596,7 +17596,7 @@
         <v>1234</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>1235</v>
@@ -17631,7 +17631,7 @@
         <v>101</v>
       </c>
       <c r="R214" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S214" s="1" t="s">
         <v>26</v>
@@ -17660,7 +17660,7 @@
         <v>1244</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>1235</v>
@@ -17691,7 +17691,7 @@
         <v>101</v>
       </c>
       <c r="R215" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S215" s="1" t="s">
         <v>26</v>
@@ -17718,10 +17718,10 @@
         <v>1253</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>1254</v>
@@ -17741,17 +17741,17 @@
         <v>1253</v>
       </c>
       <c r="N216" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="O216" s="1" t="s">
         <v>1257</v>
       </c>
       <c r="P216" s="1"/>
       <c r="Q216" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R216" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S216" s="1" t="s">
         <v>26</v>
@@ -17780,19 +17780,19 @@
         <v>1253</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>1255</v>
@@ -17807,20 +17807,20 @@
         <v>1253</v>
       </c>
       <c r="N217" s="1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="O217" s="1" t="s">
         <v>1257</v>
       </c>
       <c r="P217" s="1"/>
       <c r="Q217" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R217" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S217" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T217" s="1" t="s">
         <v>26</v>
@@ -17862,10 +17862,10 @@
         <v>1266</v>
       </c>
       <c r="K218" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M218" s="1" t="s">
         <v>1267</v>
@@ -17878,10 +17878,10 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R218" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S218" s="1" t="s">
         <v>26</v>
@@ -17936,10 +17936,10 @@
       </c>
       <c r="P219" s="1"/>
       <c r="Q219" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R219" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S219" s="1" t="s">
         <v>26</v>
@@ -17968,7 +17968,7 @@
         <v>1279</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>1146</v>
@@ -18003,7 +18003,7 @@
         <v>101</v>
       </c>
       <c r="R220" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S220" s="1" t="s">
         <v>26</v>
@@ -18032,7 +18032,7 @@
         <v>1284</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>1146</v>
@@ -18063,7 +18063,7 @@
         <v>101</v>
       </c>
       <c r="R221" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S221" s="1" t="s">
         <v>26</v>
@@ -18090,13 +18090,13 @@
         <v>1288</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>1103</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H222" s="1"/>
       <c r="I222" s="1"/>
@@ -18123,7 +18123,7 @@
         <v>51</v>
       </c>
       <c r="R222" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S222" s="1" t="s">
         <v>26</v>
@@ -18150,7 +18150,7 @@
         <v>1288</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>1103</v>
@@ -18164,7 +18164,7 @@
       <c r="K223" s="1"/>
       <c r="L223" s="1"/>
       <c r="M223" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N223" s="1"/>
       <c r="O223" s="1"/>
@@ -18177,7 +18177,7 @@
         <v>26</v>
       </c>
       <c r="T223" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U223" s="1"/>
       <c r="V223" s="1" t="s">
@@ -18213,7 +18213,7 @@
         <v>1299</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M224" s="1" t="s">
         <v>1300</v>
@@ -18229,7 +18229,7 @@
         <v>51</v>
       </c>
       <c r="R224" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S224" s="1" t="s">
         <v>26</v>
@@ -18277,7 +18277,7 @@
         <v>1306</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M225" s="1" t="s">
         <v>1307</v>
@@ -18290,10 +18290,10 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R225" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S225" s="1" t="s">
         <v>26</v>
@@ -18337,7 +18337,7 @@
         <v>1052</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M226" s="1" t="s">
         <v>1313</v>
@@ -18350,13 +18350,13 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R226" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S226" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T226" s="1" t="s">
         <v>26</v>
@@ -18397,7 +18397,7 @@
         <v>1052</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M227" s="1" t="s">
         <v>1319</v>
@@ -18410,13 +18410,13 @@
       </c>
       <c r="P227" s="1"/>
       <c r="Q227" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R227" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S227" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T227" s="1" t="s">
         <v>26</v>
@@ -18477,10 +18477,10 @@
         <v>51</v>
       </c>
       <c r="R228" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S228" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T228" s="1" t="s">
         <v>26</v>
@@ -18541,10 +18541,10 @@
         <v>51</v>
       </c>
       <c r="R229" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S229" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T229" s="1" t="s">
         <v>26</v>
@@ -18601,10 +18601,10 @@
         <v>51</v>
       </c>
       <c r="R230" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S230" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T230" s="1" t="s">
         <v>26</v>
@@ -18660,10 +18660,10 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R231" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S231" s="1" t="s">
         <v>26</v>
@@ -18723,7 +18723,7 @@
         <v>101</v>
       </c>
       <c r="R232" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S232" s="1" t="s">
         <v>26</v>
@@ -18756,13 +18756,13 @@
         <v>27</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H233" s="1" t="s">
         <v>1359</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>1360</v>
@@ -18787,7 +18787,7 @@
         <v>101</v>
       </c>
       <c r="R233" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S233" s="1" t="s">
         <v>26</v>
@@ -18832,10 +18832,10 @@
         <v>1369</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M234" s="1" t="s">
         <v>1370</v>
@@ -18851,13 +18851,13 @@
         <v>51</v>
       </c>
       <c r="R234" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S234" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T234" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U234" s="1" t="s">
         <v>1372</v>
@@ -18911,7 +18911,7 @@
         <v>51</v>
       </c>
       <c r="R235" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S235" s="1" t="s">
         <v>26</v>
@@ -18920,7 +18920,7 @@
         <v>26</v>
       </c>
       <c r="U235" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V235" s="1" t="s">
         <v>1380</v>
@@ -18976,10 +18976,10 @@
         <v>1389</v>
       </c>
       <c r="Q236" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R236" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S236" s="1" t="s">
         <v>26</v>
@@ -19027,7 +19027,7 @@
         <v>525</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M237" s="1" t="s">
         <v>1393</v>
@@ -19043,7 +19043,7 @@
         <v>101</v>
       </c>
       <c r="R237" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S237" s="1" t="s">
         <v>26</v>
@@ -19088,7 +19088,7 @@
         <v>1402</v>
       </c>
       <c r="K238" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L238" s="1" t="s">
         <v>1403</v>
@@ -19107,7 +19107,7 @@
         <v>51</v>
       </c>
       <c r="R238" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S238" s="1" t="s">
         <v>26</v>
@@ -19157,7 +19157,7 @@
         <v>1410</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M239" s="1" t="s">
         <v>1411</v>
@@ -19173,7 +19173,7 @@
         <v>51</v>
       </c>
       <c r="R239" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S239" s="1" t="s">
         <v>26</v>
@@ -19218,7 +19218,7 @@
         <v>1419</v>
       </c>
       <c r="K240" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L240" s="1" t="s">
         <v>1378</v>
@@ -19237,13 +19237,13 @@
         <v>101</v>
       </c>
       <c r="R240" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S240" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T240" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U240" s="1" t="s">
         <v>1422</v>
@@ -19295,7 +19295,7 @@
         <v>101</v>
       </c>
       <c r="R241" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S241" s="1" t="s">
         <v>26</v>
@@ -19355,7 +19355,7 @@
         <v>51</v>
       </c>
       <c r="R242" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S242" s="1" t="s">
         <v>26</v>
@@ -19384,7 +19384,7 @@
         <v>1335</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>220</v>
@@ -19414,10 +19414,10 @@
       </c>
       <c r="P243" s="1"/>
       <c r="Q243" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R243" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S243" s="1" t="s">
         <v>26</v>
@@ -19478,10 +19478,10 @@
       </c>
       <c r="P244" s="1"/>
       <c r="Q244" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R244" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S244" s="1" t="s">
         <v>26</v>
@@ -19542,10 +19542,10 @@
       </c>
       <c r="P245" s="1"/>
       <c r="Q245" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R245" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S245" s="1" t="s">
         <v>26</v>
@@ -19608,10 +19608,10 @@
         <v>26</v>
       </c>
       <c r="S246" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T246" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U246" s="1" t="s">
         <v>62</v>
@@ -19646,10 +19646,10 @@
         <v>1462</v>
       </c>
       <c r="K247" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="M247" s="1" t="s">
         <v>1461</v>
@@ -19665,7 +19665,7 @@
         <v>101</v>
       </c>
       <c r="R247" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S247" s="1" t="s">
         <v>26</v>
@@ -19706,10 +19706,10 @@
         <v>1468</v>
       </c>
       <c r="K248" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1467</v>
@@ -19722,10 +19722,10 @@
       </c>
       <c r="P248" s="1"/>
       <c r="Q248" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R248" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S248" s="1" t="s">
         <v>26</v>
@@ -19758,22 +19758,22 @@
         <v>27</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>1468</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>1472</v>
@@ -19786,10 +19786,10 @@
       </c>
       <c r="P249" s="1"/>
       <c r="Q249" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R249" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S249" s="1" t="s">
         <v>26</v>
@@ -19851,13 +19851,13 @@
         <v>51</v>
       </c>
       <c r="R250" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S250" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T250" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U250" s="1" t="s">
         <v>1372</v>
@@ -19899,7 +19899,7 @@
         <v>1489</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M251" s="1" t="s">
         <v>1485</v>
@@ -19912,10 +19912,10 @@
       </c>
       <c r="P251" s="1"/>
       <c r="Q251" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R251" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S251" s="1" t="s">
         <v>26</v>
@@ -19958,10 +19958,10 @@
         <v>1497</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M252" s="1" t="s">
         <v>1495</v>
@@ -19977,7 +19977,7 @@
         <v>101</v>
       </c>
       <c r="R252" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S252" s="1" t="s">
         <v>26</v>
@@ -20020,10 +20020,10 @@
         <v>1501</v>
       </c>
       <c r="K253" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M253" s="1" t="s">
         <v>1495</v>
@@ -20039,7 +20039,7 @@
         <v>101</v>
       </c>
       <c r="R253" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S253" s="1" t="s">
         <v>26</v>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="P254" s="1"/>
       <c r="Q254" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R254" s="1" t="s">
         <v>26</v>
@@ -20159,7 +20159,7 @@
         <v>101</v>
       </c>
       <c r="R255" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S255" s="1" t="s">
         <v>26</v>
@@ -20168,7 +20168,7 @@
         <v>26</v>
       </c>
       <c r="U255" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V255" s="1" t="s">
         <v>1520</v>
@@ -20200,10 +20200,10 @@
         <v>1524</v>
       </c>
       <c r="K256" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M256" s="1" t="s">
         <v>1523</v>
@@ -20216,10 +20216,10 @@
       </c>
       <c r="P256" s="1"/>
       <c r="Q256" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R256" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S256" s="1" t="s">
         <v>26</v>
@@ -20260,10 +20260,10 @@
         <v>1524</v>
       </c>
       <c r="K257" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M257" s="1" t="s">
         <v>1528</v>
@@ -20276,10 +20276,10 @@
       </c>
       <c r="P257" s="1"/>
       <c r="Q257" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R257" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S257" s="1" t="s">
         <v>26</v>
@@ -20322,7 +20322,7 @@
         <v>1534</v>
       </c>
       <c r="K258" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L258" s="1" t="s">
         <v>1531</v>
@@ -20338,10 +20338,10 @@
       </c>
       <c r="P258" s="1"/>
       <c r="Q258" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R258" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S258" s="1" t="s">
         <v>26</v>
@@ -20380,7 +20380,7 @@
         <v>1534</v>
       </c>
       <c r="K259" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L259" s="1"/>
       <c r="M259" s="1" t="s">
@@ -20396,7 +20396,7 @@
         <v>1540</v>
       </c>
       <c r="Q259" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R259" s="1" t="s">
         <v>26</v>
@@ -20405,7 +20405,7 @@
         <v>26</v>
       </c>
       <c r="T259" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U259" s="1" t="s">
         <v>665</v>
@@ -20456,10 +20456,10 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R260" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S260" s="1" t="s">
         <v>26</v>
@@ -20516,10 +20516,10 @@
       </c>
       <c r="P261" s="1"/>
       <c r="Q261" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R261" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S261" s="1" t="s">
         <v>26</v>
@@ -20581,7 +20581,7 @@
         <v>101</v>
       </c>
       <c r="R262" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S262" s="1" t="s">
         <v>26</v>
@@ -20645,7 +20645,7 @@
         <v>101</v>
       </c>
       <c r="R263" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S263" s="1" t="s">
         <v>26</v>
@@ -20674,7 +20674,7 @@
         <v>1572</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>1573</v>
@@ -20705,7 +20705,7 @@
         <v>101</v>
       </c>
       <c r="R264" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S264" s="1" t="s">
         <v>26</v>
@@ -20732,7 +20732,7 @@
         <v>1579</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>1580</v>
@@ -20766,10 +20766,10 @@
       </c>
       <c r="P265" s="1"/>
       <c r="Q265" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R265" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S265" s="1" t="s">
         <v>26</v>
@@ -20808,10 +20808,10 @@
         <v>1588</v>
       </c>
       <c r="K266" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M266" s="1" t="s">
         <v>1589</v>
@@ -20824,10 +20824,10 @@
       </c>
       <c r="P266" s="1"/>
       <c r="Q266" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R266" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S266" s="1" t="s">
         <v>26</v>
@@ -20862,13 +20862,13 @@
         <v>27</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>1594</v>
@@ -20893,7 +20893,7 @@
         <v>51</v>
       </c>
       <c r="R267" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S267" s="1" t="s">
         <v>26</v>
@@ -20953,7 +20953,7 @@
         <v>101</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S268" s="1" t="s">
         <v>26</v>
@@ -21001,7 +21001,7 @@
         <v>1612</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1613</v>
@@ -21017,7 +21017,7 @@
         <v>101</v>
       </c>
       <c r="R269" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S269" s="1" t="s">
         <v>26</v>
@@ -21026,7 +21026,7 @@
         <v>26</v>
       </c>
       <c r="U269" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V269" s="1" t="s">
         <v>1615</v>
@@ -21076,10 +21076,10 @@
       </c>
       <c r="P270" s="1"/>
       <c r="Q270" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R270" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S270" s="1" t="s">
         <v>26</v>
@@ -21138,10 +21138,10 @@
       </c>
       <c r="P271" s="1"/>
       <c r="Q271" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R271" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S271" s="1" t="s">
         <v>26</v>
@@ -21191,7 +21191,7 @@
         <v>59</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M272" s="1" t="s">
         <v>1630</v>
@@ -21204,7 +21204,7 @@
       </c>
       <c r="P272" s="1"/>
       <c r="Q272" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R272" s="1" t="s">
         <v>26</v>
@@ -21213,7 +21213,7 @@
         <v>26</v>
       </c>
       <c r="T272" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U272" s="1" t="s">
         <v>1636</v>
@@ -21255,7 +21255,7 @@
         <v>59</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M273" s="1" t="s">
         <v>1639</v>
@@ -21268,10 +21268,10 @@
       </c>
       <c r="P273" s="1"/>
       <c r="Q273" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R273" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S273" s="1" t="s">
         <v>26</v>
@@ -21298,19 +21298,19 @@
         <v>1645</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>220</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H274" s="1" t="s">
         <v>1646</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>1647</v>
@@ -21337,7 +21337,7 @@
         <v>101</v>
       </c>
       <c r="R274" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S274" s="1" t="s">
         <v>26</v>
@@ -21364,19 +21364,19 @@
         <v>1653</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>220</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H275" s="1" t="s">
         <v>1646</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>1647</v>
@@ -21403,7 +21403,7 @@
         <v>101</v>
       </c>
       <c r="R275" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S275" s="1" t="s">
         <v>26</v>
@@ -21465,7 +21465,7 @@
         <v>51</v>
       </c>
       <c r="R276" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S276" s="1" t="s">
         <v>26</v>
@@ -21474,7 +21474,7 @@
         <v>26</v>
       </c>
       <c r="U276" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V276" s="1" t="s">
         <v>1663</v>
@@ -21529,7 +21529,7 @@
         <v>101</v>
       </c>
       <c r="R277" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S277" s="1" t="s">
         <v>26</v>
@@ -21538,7 +21538,7 @@
         <v>26</v>
       </c>
       <c r="U277" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V277" s="1" t="s">
         <v>1670</v>
@@ -21558,7 +21558,7 @@
         <v>1279</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>1248</v>
@@ -21593,7 +21593,7 @@
         <v>101</v>
       </c>
       <c r="R278" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S278" s="1" t="s">
         <v>26</v>
@@ -21622,7 +21622,7 @@
         <v>1677</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>1248</v>
@@ -21653,7 +21653,7 @@
         <v>101</v>
       </c>
       <c r="R279" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S279" s="1" t="s">
         <v>26</v>
@@ -21694,7 +21694,7 @@
         <v>1683</v>
       </c>
       <c r="K280" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L280" s="1" t="s">
         <v>214</v>
@@ -21710,10 +21710,10 @@
       </c>
       <c r="P280" s="1"/>
       <c r="Q280" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R280" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S280" s="1" t="s">
         <v>26</v>
@@ -21773,7 +21773,7 @@
         <v>51</v>
       </c>
       <c r="R281" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S281" s="1" t="s">
         <v>26</v>
@@ -21832,10 +21832,10 @@
       </c>
       <c r="P282" s="1"/>
       <c r="Q282" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R282" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S282" s="1" t="s">
         <v>26</v>
@@ -21899,7 +21899,7 @@
         <v>51</v>
       </c>
       <c r="R283" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S283" s="1" t="s">
         <v>26</v>
@@ -21908,7 +21908,7 @@
         <v>26</v>
       </c>
       <c r="U283" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V283" s="1" t="s">
         <v>1709</v>
@@ -21958,10 +21958,10 @@
       </c>
       <c r="P284" s="1"/>
       <c r="Q284" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R284" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S284" s="1" t="s">
         <v>26</v>
@@ -21970,7 +21970,7 @@
         <v>26</v>
       </c>
       <c r="U284" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V284" s="1" t="s">
         <v>1719</v>
@@ -21990,7 +21990,7 @@
         <v>1721</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>71</v>
@@ -22002,7 +22002,7 @@
       <c r="K285" s="1"/>
       <c r="L285" s="1"/>
       <c r="M285" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
@@ -22015,7 +22015,7 @@
         <v>26</v>
       </c>
       <c r="T285" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U285" s="1"/>
       <c r="V285" s="1" t="s">
@@ -22069,13 +22069,13 @@
         <v>51</v>
       </c>
       <c r="R286" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S286" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T286" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U286" s="1" t="s">
         <v>1732</v>
@@ -22137,7 +22137,7 @@
         <v>51</v>
       </c>
       <c r="R287" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S287" s="1" t="s">
         <v>26</v>
